--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshi\FMKyuyo\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D96B75-41DC-437A-9EA5-7290A7DE7680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064D9F98-31E4-457E-AF2B-820C42EC6E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8295" yWindow="2925" windowWidth="28800" windowHeight="16110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1140" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$151</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="156">
   <si>
     <t>ClassName</t>
   </si>
@@ -345,20 +345,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ShowBank</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>銀行情報</t>
-    <rPh sb="0" eb="2">
-      <t>ギンコウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncFixedKyuyo</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -721,21 +707,6 @@
   </si>
   <si>
     <t>FuncMyno_DlgEntryPWD</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ShowMynoPWD</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F8</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>マイナンバーパスワード変更</t>
-    <rPh sb="11" eb="13">
-      <t>ヘンコウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1263,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -1300,14 +1271,14 @@
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -1316,46 +1287,46 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -1364,14 +1335,14 @@
         <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -1380,78 +1351,78 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -1460,14 +1431,14 @@
         <v>29</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -1476,78 +1447,78 @@
         <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -1556,14 +1527,14 @@
         <v>31</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F18" s="4"/>
     </row>
@@ -1572,14 +1543,14 @@
         <v>31</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -1588,174 +1559,174 @@
         <v>31</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="F30" s="4"/>
     </row>
@@ -1764,14 +1735,14 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1780,110 +1751,110 @@
         <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>7</v>
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>11</v>
+        <v>45</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>7</v>
+        <v>45</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1891,47 +1862,47 @@
       <c r="A39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>38</v>
+      <c r="B39" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>137</v>
+        <v>47</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="F41" s="4"/>
     </row>
@@ -1940,14 +1911,14 @@
         <v>47</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="F42" s="4"/>
     </row>
@@ -1956,14 +1927,14 @@
         <v>47</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F43" s="4"/>
     </row>
@@ -1972,14 +1943,14 @@
         <v>47</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F44" s="4"/>
     </row>
@@ -1988,14 +1959,14 @@
         <v>47</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F45" s="4"/>
     </row>
@@ -2003,11 +1974,11 @@
       <c r="A46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>48</v>
+      <c r="B46" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
@@ -2020,14 +1991,14 @@
         <v>47</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F47" s="4"/>
     </row>
@@ -2035,15 +2006,15 @@
       <c r="A48" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>49</v>
+      <c r="B48" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F48" s="4"/>
     </row>
@@ -2051,11 +2022,11 @@
       <c r="A49" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>101</v>
+      <c r="B49" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
@@ -2068,78 +2039,78 @@
         <v>47</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" s="4"/>
     </row>
@@ -2148,20 +2119,20 @@
         <v>63</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>11</v>
@@ -2177,7 +2148,7 @@
     </row>
     <row r="57" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>7</v>
@@ -2193,33 +2164,33 @@
     </row>
     <row r="58" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F59" s="4"/>
     </row>
@@ -2228,14 +2199,14 @@
         <v>65</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F60" s="4"/>
     </row>
@@ -2244,46 +2215,46 @@
         <v>65</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F63" s="4"/>
     </row>
@@ -2292,180 +2263,180 @@
         <v>66</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>7</v>
+        <v>67</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="D66" s="6"/>
-      <c r="E66" s="6" t="s">
-        <v>9</v>
+      <c r="E66" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D68" s="6"/>
-      <c r="E68" s="4" t="s">
-        <v>72</v>
+      <c r="E68" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>11</v>
@@ -2481,7 +2452,7 @@
     </row>
     <row r="76" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>7</v>
@@ -2497,93 +2468,93 @@
     </row>
     <row r="77" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="6" t="s">
-        <v>6</v>
+      <c r="E77" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D79" s="6"/>
-      <c r="E79" s="4" t="s">
-        <v>72</v>
+      <c r="E79" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>19</v>
+        <v>89</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6" t="s">
@@ -2593,279 +2564,279 @@
     </row>
     <row r="83" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F94" s="4"/>
     </row>
     <row r="95" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F96" s="4"/>
     </row>
     <row r="97" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>11</v>
+        <v>113</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="F97" s="4"/>
     </row>
     <row r="98" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>7</v>
+        <v>113</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F99" s="4"/>
     </row>
     <row r="100" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>19</v>
@@ -2875,141 +2846,141 @@
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="F102" s="4"/>
     </row>
     <row r="103" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="F103" s="4"/>
     </row>
     <row r="104" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="6" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="F104" s="4"/>
     </row>
     <row r="105" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="F105" s="4"/>
     </row>
     <row r="106" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="F106" s="4"/>
     </row>
     <row r="107" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="F107" s="4"/>
     </row>
     <row r="108" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>19</v>
+        <v>130</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F108" s="4"/>
     </row>
     <row r="109" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>11</v>
@@ -3025,7 +2996,7 @@
     </row>
     <row r="110" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>7</v>
@@ -3043,15 +3014,15 @@
       <c r="A111" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B111" s="4" t="s">
-        <v>11</v>
+      <c r="B111" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="F111" s="4"/>
     </row>
@@ -3073,167 +3044,167 @@
     </row>
     <row r="113" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>7</v>
+        <v>137</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F114" s="4"/>
     </row>
     <row r="115" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>112</v>
+        <v>138</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="F115" s="4"/>
     </row>
     <row r="116" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>19</v>
+        <v>138</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F116" s="4"/>
     </row>
     <row r="117" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F117" s="4"/>
     </row>
     <row r="118" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F118" s="4"/>
     </row>
     <row r="119" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="F119" s="4"/>
     </row>
     <row r="120" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F120" s="4"/>
     </row>
     <row r="121" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="F121" s="4"/>
     </row>
     <row r="122" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>11</v>
+        <v>142</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F122" s="4"/>
     </row>
     <row r="123" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>7</v>
@@ -3249,33 +3220,33 @@
     </row>
     <row r="124" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F124" s="4"/>
     </row>
     <row r="125" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>7</v>
+        <v>143</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F125" s="4"/>
     </row>
@@ -3283,15 +3254,15 @@
       <c r="A126" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>38</v>
+      <c r="B126" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F126" s="4"/>
     </row>
@@ -3300,255 +3271,239 @@
         <v>148</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="F127" s="4"/>
     </row>
     <row r="128" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="F128" s="4"/>
     </row>
     <row r="129" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="6" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="F129" s="4"/>
     </row>
     <row r="130" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>19</v>
+        <v>151</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F130" s="4"/>
     </row>
     <row r="131" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F131" s="4"/>
     </row>
     <row r="132" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F132" s="4"/>
     </row>
     <row r="133" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>19</v>
+        <v>152</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F134" s="4"/>
     </row>
     <row r="135" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F135" s="4"/>
     </row>
     <row r="136" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F136" s="4"/>
     </row>
     <row r="137" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F138" s="4"/>
     </row>
     <row r="139" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F139" s="4"/>
     </row>
     <row r="140" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="5"/>
       <c r="D141" s="6"/>
-      <c r="E141" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E141" s="6"/>
       <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="5"/>
       <c r="D142" s="6"/>
-      <c r="E142" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E142" s="6"/>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4375,24 +4330,8 @@
       <c r="E245" s="6"/>
       <c r="F245" s="4"/>
     </row>
-    <row r="246" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A246" s="3"/>
-      <c r="B246" s="3"/>
-      <c r="C246" s="5"/>
-      <c r="D246" s="6"/>
-      <c r="E246" s="6"/>
-      <c r="F246" s="4"/>
-    </row>
-    <row r="247" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A247" s="3"/>
-      <c r="B247" s="3"/>
-      <c r="C247" s="5"/>
-      <c r="D247" s="6"/>
-      <c r="E247" s="6"/>
-      <c r="F247" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F153" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F151" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064D9F98-31E4-457E-AF2B-820C42EC6E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565B1A02-6F33-4F76-93FD-ABE5A8B8807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38430" windowHeight="15690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="160">
   <si>
     <t>ClassName</t>
   </si>
@@ -830,6 +830,21 @@
   </si>
   <si>
     <t>FuncMasterBankCode_DlgEntry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterKaihi</t>
+  </si>
+  <si>
+    <t>FuncMasterKaihi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterKaihi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterKaihi_DlgEntry</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -905,7 +920,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -928,6 +943,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3491,51 +3509,99 @@
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="5"/>
+      <c r="A141" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="4"/>
+      <c r="E141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F141" s="10"/>
     </row>
     <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="5"/>
+      <c r="A142" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
+      <c r="E142" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
-      <c r="C143" s="5"/>
+      <c r="A143" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
+      <c r="E143" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="F143" s="4"/>
     </row>
     <row r="144" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="5"/>
+      <c r="A144" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
+      <c r="E144" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="5"/>
+      <c r="A145" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
+      <c r="E145" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="5"/>
+      <c r="A146" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
+      <c r="E146" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565B1A02-6F33-4F76-93FD-ABE5A8B8807B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF7DE63-9DF1-40ED-B7FD-0575D391DBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38430" windowHeight="15690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="510" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="162">
   <si>
     <t>ClassName</t>
   </si>
@@ -845,6 +845,14 @@
   </si>
   <si>
     <t>FuncMasterKaihi_DlgEntry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterIryoKikan_DlgEntry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterIryoKikan</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -920,7 +928,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -943,9 +951,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3522,7 +3527,7 @@
       <c r="E141" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F141" s="10"/>
+      <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="3" t="s">
@@ -3605,59 +3610,102 @@
       <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="5"/>
+      <c r="A147" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
+      <c r="E147" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F147" s="4"/>
     </row>
     <row r="148" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="5"/>
+      <c r="A148" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
+      <c r="E148" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="5"/>
+      <c r="A149" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
+      <c r="E149" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
-      <c r="C150" s="5"/>
+      <c r="A150" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
+      <c r="E150" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="5"/>
+      <c r="A151" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
+      <c r="E151" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
-      <c r="C152" s="5"/>
+      <c r="A152" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
+      <c r="E152" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
-      <c r="C153" s="5"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF7DE63-9DF1-40ED-B7FD-0575D391DBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC3B40F-21F1-4F1B-B914-4BC7C6C68947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="510" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$147</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="155">
   <si>
     <t>ClassName</t>
   </si>
@@ -639,23 +639,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Print</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一覧表印刷</t>
-    <rPh sb="0" eb="2">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>インサツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncStaff_DlgPrint</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -691,17 +674,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ShowMyno</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>マイナンバー管理</t>
-    <rPh sb="6" eb="8">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncStaff_DlgMyno</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -770,24 +742,6 @@
     <t>作成実行</t>
     <rPh sb="0" eb="4">
       <t>サクセイジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ShowTeishutsusaki</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F7</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>提出先マスター</t>
-    <rPh sb="0" eb="2">
-      <t>テイシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>サキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1257,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F245"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -1627,7 +1581,7 @@
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -1643,7 +1597,7 @@
     </row>
     <row r="24" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>17</v>
@@ -1659,7 +1613,7 @@
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>18</v>
@@ -1675,87 +1629,87 @@
     </row>
     <row r="26" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>128</v>
+        <v>37</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>11</v>
@@ -1771,7 +1725,7 @@
     </row>
     <row r="32" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>7</v>
@@ -1787,13 +1741,13 @@
     </row>
     <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
@@ -1803,97 +1757,97 @@
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>132</v>
+        <v>47</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1902,14 +1856,14 @@
         <v>47</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1918,14 +1872,14 @@
         <v>47</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="F41" s="4"/>
     </row>
@@ -1933,15 +1887,15 @@
       <c r="A42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>53</v>
+      <c r="B42" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="F42" s="4"/>
     </row>
@@ -1950,14 +1904,14 @@
         <v>47</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="F43" s="4"/>
     </row>
@@ -1966,14 +1920,14 @@
         <v>47</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F44" s="4"/>
     </row>
@@ -1981,15 +1935,15 @@
       <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>100</v>
+      <c r="B45" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F45" s="4"/>
     </row>
@@ -1997,341 +1951,341 @@
       <c r="A46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>49</v>
+      <c r="B46" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>102</v>
+        <v>63</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F54" s="4"/>
     </row>
     <row r="55" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F56" s="4"/>
     </row>
     <row r="57" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D62" s="6"/>
-      <c r="E62" s="6" t="s">
-        <v>79</v>
+      <c r="E62" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D66" s="6"/>
-      <c r="E66" s="4" t="s">
-        <v>70</v>
+      <c r="E66" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>19</v>
@@ -2347,425 +2301,425 @@
     </row>
     <row r="68" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>11</v>
+        <v>77</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D73" s="6"/>
-      <c r="E73" s="6" t="s">
-        <v>6</v>
+      <c r="E73" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>7</v>
+        <v>89</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="4" t="s">
-        <v>70</v>
+      <c r="E77" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>81</v>
+        <v>94</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>18</v>
+        <v>113</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B94" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C94" s="5" t="s">
@@ -2773,45 +2727,45 @@
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="F94" s="4"/>
     </row>
     <row r="95" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>11</v>
+        <v>116</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>7</v>
+        <v>116</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F96" s="4"/>
     </row>
     <row r="97" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>110</v>
@@ -2821,173 +2775,173 @@
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F97" s="4"/>
     </row>
     <row r="98" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="F99" s="4"/>
     </row>
     <row r="100" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="F102" s="4"/>
     </row>
     <row r="103" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>19</v>
+        <v>126</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F103" s="4"/>
     </row>
     <row r="104" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="6" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="F104" s="4"/>
     </row>
     <row r="105" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="F105" s="4"/>
     </row>
     <row r="106" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>19</v>
+        <v>127</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F106" s="4"/>
     </row>
     <row r="107" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="C107" s="5" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6" t="s">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="F107" s="4"/>
     </row>
     <row r="108" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>7</v>
@@ -3003,89 +2957,89 @@
     </row>
     <row r="109" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>11</v>
+        <v>133</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="F109" s="4"/>
     </row>
     <row r="110" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>7</v>
+        <v>133</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F110" s="4"/>
     </row>
     <row r="111" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B111" s="3" t="s">
         <v>134</v>
       </c>
+      <c r="B111" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="C111" s="5" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="F111" s="4"/>
     </row>
     <row r="112" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F112" s="4"/>
     </row>
     <row r="113" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>110</v>
+        <v>134</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B114" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C114" s="5" t="s">
@@ -3099,49 +3053,49 @@
     </row>
     <row r="115" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="F115" s="4"/>
     </row>
     <row r="116" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F116" s="4"/>
     </row>
     <row r="117" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F117" s="4"/>
     </row>
@@ -3149,31 +3103,31 @@
       <c r="A118" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B118" s="4" t="s">
-        <v>19</v>
+      <c r="B118" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F118" s="4"/>
     </row>
     <row r="119" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6" t="s">
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="F119" s="4"/>
     </row>
@@ -3181,15 +3135,15 @@
       <c r="A120" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>11</v>
+      <c r="B120" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6" t="s">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="F120" s="4"/>
     </row>
@@ -3197,117 +3151,117 @@
       <c r="A121" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>7</v>
+      <c r="B121" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F121" s="4"/>
     </row>
     <row r="122" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="C122" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6" t="s">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="F122" s="4"/>
     </row>
     <row r="123" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>7</v>
+        <v>141</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6" t="s">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="F123" s="4"/>
     </row>
     <row r="124" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="F124" s="4"/>
     </row>
     <row r="125" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>19</v>
+        <v>144</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F125" s="4"/>
     </row>
     <row r="126" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>149</v>
+        <v>17</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="F126" s="4"/>
     </row>
     <row r="127" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="F127" s="4"/>
     </row>
     <row r="128" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>19</v>
@@ -3323,389 +3277,357 @@
     </row>
     <row r="129" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F129" s="4"/>
     </row>
     <row r="130" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F130" s="4"/>
     </row>
     <row r="131" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F131" s="4"/>
     </row>
     <row r="132" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>19</v>
+        <v>147</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F132" s="4"/>
     </row>
     <row r="133" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F134" s="4"/>
     </row>
     <row r="135" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F135" s="4"/>
     </row>
     <row r="136" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F136" s="4"/>
     </row>
     <row r="137" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F138" s="4"/>
     </row>
     <row r="139" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F139" s="4"/>
     </row>
     <row r="140" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F143" s="4"/>
     </row>
     <row r="144" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F147" s="4"/>
     </row>
     <row r="148" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="6"/>
-      <c r="E150" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="E150" s="6"/>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="5"/>
       <c r="D151" s="6"/>
-      <c r="E151" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="E151" s="6"/>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="5"/>
       <c r="D152" s="6"/>
-      <c r="E152" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E152" s="6"/>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4412,40 +4334,8 @@
       <c r="E241" s="6"/>
       <c r="F241" s="4"/>
     </row>
-    <row r="242" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A242" s="3"/>
-      <c r="B242" s="3"/>
-      <c r="C242" s="5"/>
-      <c r="D242" s="6"/>
-      <c r="E242" s="6"/>
-      <c r="F242" s="4"/>
-    </row>
-    <row r="243" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A243" s="3"/>
-      <c r="B243" s="3"/>
-      <c r="C243" s="5"/>
-      <c r="D243" s="6"/>
-      <c r="E243" s="6"/>
-      <c r="F243" s="4"/>
-    </row>
-    <row r="244" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A244" s="3"/>
-      <c r="B244" s="3"/>
-      <c r="C244" s="5"/>
-      <c r="D244" s="6"/>
-      <c r="E244" s="6"/>
-      <c r="F244" s="4"/>
-    </row>
-    <row r="245" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A245" s="3"/>
-      <c r="B245" s="3"/>
-      <c r="C245" s="5"/>
-      <c r="D245" s="6"/>
-      <c r="E245" s="6"/>
-      <c r="F245" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F151" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>
